--- a/excel/mull-trans/Raspored_Koska_Zona59_2026.xlsx
+++ b/excel/mull-trans/Raspored_Koska_Zona59_2026.xlsx
@@ -12,8 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Po vrsti" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Raspored'!$A$4:$H$43</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Po vrsti'!$A$1:$D$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Raspored'!$A$4:$H$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Po vrsti'!$A$1:$D$40</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -663,7 +663,7 @@
         </is>
       </c>
       <c r="B6" s="6">
-        <f>IFERROR(1/(1/_xlfn.MINIFS(Raspored!$A$5:$A$43,Raspored!$D$5:$D$43,"x",Raspored!$A$5:$A$43,"&gt;="&amp;$B$3)),"nema više u 2026.")</f>
+        <f>IFERROR(1/(1/_xlfn.MINIFS(Raspored!$A$5:$A$34,Raspored!$D$5:$D$34,"x",Raspored!$A$5:$A$34,"&gt;="&amp;$B$3)),"nema više u 2026.")</f>
         <v/>
       </c>
       <c r="C6" s="7">
@@ -675,7 +675,7 @@
         <v/>
       </c>
       <c r="E6" s="7">
-        <f>COUNTIF(Raspored!$D$5:$D$43,"x")</f>
+        <f>COUNTIF(Raspored!$D$5:$D$34,"x")</f>
         <v/>
       </c>
     </row>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="B7" s="6">
-        <f>IFERROR(1/(1/_xlfn.MINIFS(Raspored!$A$5:$A$43,Raspored!$E$5:$E$43,"x",Raspored!$A$5:$A$43,"&gt;="&amp;$B$3)),"nema više u 2026.")</f>
+        <f>IFERROR(1/(1/_xlfn.MINIFS(Raspored!$A$5:$A$34,Raspored!$E$5:$E$34,"x",Raspored!$A$5:$A$34,"&gt;="&amp;$B$3)),"nema više u 2026.")</f>
         <v/>
       </c>
       <c r="C7" s="7">
@@ -698,7 +698,7 @@
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>COUNTIF(Raspored!$E$5:$E$43,"x")</f>
+        <f>COUNTIF(Raspored!$E$5:$E$34,"x")</f>
         <v/>
       </c>
     </row>
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="B8" s="6">
-        <f>IFERROR(1/(1/_xlfn.MINIFS(Raspored!$A$5:$A$43,Raspored!$F$5:$F$43,"x",Raspored!$A$5:$A$43,"&gt;="&amp;$B$3)),"nema više u 2026.")</f>
+        <f>IFERROR(1/(1/_xlfn.MINIFS(Raspored!$A$5:$A$34,Raspored!$F$5:$F$34,"x",Raspored!$A$5:$A$34,"&gt;="&amp;$B$3)),"nema više u 2026.")</f>
         <v/>
       </c>
       <c r="C8" s="7">
@@ -721,7 +721,7 @@
         <v/>
       </c>
       <c r="E8" s="7">
-        <f>COUNTIF(Raspored!$F$5:$F$43,"x")</f>
+        <f>COUNTIF(Raspored!$F$5:$F$34,"x")</f>
         <v/>
       </c>
     </row>
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="B9" s="6">
-        <f>IFERROR(1/(1/_xlfn.MINIFS(Raspored!$A$5:$A$43,Raspored!$G$5:$G$43,"x",Raspored!$A$5:$A$43,"&gt;="&amp;$B$3)),"nema više u 2026.")</f>
+        <f>IFERROR(1/(1/_xlfn.MINIFS(Raspored!$A$5:$A$34,Raspored!$G$5:$G$34,"x",Raspored!$A$5:$A$34,"&gt;="&amp;$B$3)),"nema više u 2026.")</f>
         <v/>
       </c>
       <c r="C9" s="7">
@@ -744,7 +744,7 @@
         <v/>
       </c>
       <c r="E9" s="7">
-        <f>COUNTIF(Raspored!$G$5:$G$43,"x")</f>
+        <f>COUNTIF(Raspored!$G$5:$G$34,"x")</f>
         <v/>
       </c>
     </row>
@@ -789,19 +789,19 @@
         </is>
       </c>
       <c r="B13" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$43,$A13,Raspored!$D$5:$D$43,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$34,$A13,Raspored!$D$5:$D$34,"x")</f>
         <v/>
       </c>
       <c r="C13" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$43,$A13,Raspored!$E$5:$E$43,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$34,$A13,Raspored!$E$5:$E$34,"x")</f>
         <v/>
       </c>
       <c r="D13" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$43,$A13,Raspored!$F$5:$F$43,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$34,$A13,Raspored!$F$5:$F$34,"x")</f>
         <v/>
       </c>
       <c r="E13" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$43,$A13,Raspored!$G$5:$G$43,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$34,$A13,Raspored!$G$5:$G$34,"x")</f>
         <v/>
       </c>
     </row>
@@ -812,19 +812,19 @@
         </is>
       </c>
       <c r="B14" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$43,$A14,Raspored!$D$5:$D$43,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$34,$A14,Raspored!$D$5:$D$34,"x")</f>
         <v/>
       </c>
       <c r="C14" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$43,$A14,Raspored!$E$5:$E$43,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$34,$A14,Raspored!$E$5:$E$34,"x")</f>
         <v/>
       </c>
       <c r="D14" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$43,$A14,Raspored!$F$5:$F$43,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$34,$A14,Raspored!$F$5:$F$34,"x")</f>
         <v/>
       </c>
       <c r="E14" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$43,$A14,Raspored!$G$5:$G$43,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$34,$A14,Raspored!$G$5:$G$34,"x")</f>
         <v/>
       </c>
     </row>
@@ -835,19 +835,19 @@
         </is>
       </c>
       <c r="B15" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$43,$A15,Raspored!$D$5:$D$43,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$34,$A15,Raspored!$D$5:$D$34,"x")</f>
         <v/>
       </c>
       <c r="C15" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$43,$A15,Raspored!$E$5:$E$43,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$34,$A15,Raspored!$E$5:$E$34,"x")</f>
         <v/>
       </c>
       <c r="D15" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$43,$A15,Raspored!$F$5:$F$43,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$34,$A15,Raspored!$F$5:$F$34,"x")</f>
         <v/>
       </c>
       <c r="E15" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$43,$A15,Raspored!$G$5:$G$43,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$34,$A15,Raspored!$G$5:$G$34,"x")</f>
         <v/>
       </c>
     </row>
@@ -858,19 +858,19 @@
         </is>
       </c>
       <c r="B16" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$43,$A16,Raspored!$D$5:$D$43,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$34,$A16,Raspored!$D$5:$D$34,"x")</f>
         <v/>
       </c>
       <c r="C16" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$43,$A16,Raspored!$E$5:$E$43,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$34,$A16,Raspored!$E$5:$E$34,"x")</f>
         <v/>
       </c>
       <c r="D16" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$43,$A16,Raspored!$F$5:$F$43,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$34,$A16,Raspored!$F$5:$F$34,"x")</f>
         <v/>
       </c>
       <c r="E16" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$43,$A16,Raspored!$G$5:$G$43,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$34,$A16,Raspored!$G$5:$G$34,"x")</f>
         <v/>
       </c>
     </row>
@@ -881,19 +881,19 @@
         </is>
       </c>
       <c r="B17" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$43,$A17,Raspored!$D$5:$D$43,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$34,$A17,Raspored!$D$5:$D$34,"x")</f>
         <v/>
       </c>
       <c r="C17" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$43,$A17,Raspored!$E$5:$E$43,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$34,$A17,Raspored!$E$5:$E$34,"x")</f>
         <v/>
       </c>
       <c r="D17" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$43,$A17,Raspored!$F$5:$F$43,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$34,$A17,Raspored!$F$5:$F$34,"x")</f>
         <v/>
       </c>
       <c r="E17" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$43,$A17,Raspored!$G$5:$G$43,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$34,$A17,Raspored!$G$5:$G$34,"x")</f>
         <v/>
       </c>
     </row>
@@ -904,19 +904,19 @@
         </is>
       </c>
       <c r="B18" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$43,$A18,Raspored!$D$5:$D$43,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$34,$A18,Raspored!$D$5:$D$34,"x")</f>
         <v/>
       </c>
       <c r="C18" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$43,$A18,Raspored!$E$5:$E$43,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$34,$A18,Raspored!$E$5:$E$34,"x")</f>
         <v/>
       </c>
       <c r="D18" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$43,$A18,Raspored!$F$5:$F$43,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$34,$A18,Raspored!$F$5:$F$34,"x")</f>
         <v/>
       </c>
       <c r="E18" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$43,$A18,Raspored!$G$5:$G$43,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$34,$A18,Raspored!$G$5:$G$34,"x")</f>
         <v/>
       </c>
     </row>
@@ -927,19 +927,19 @@
         </is>
       </c>
       <c r="B19" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$43,$A19,Raspored!$D$5:$D$43,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$34,$A19,Raspored!$D$5:$D$34,"x")</f>
         <v/>
       </c>
       <c r="C19" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$43,$A19,Raspored!$E$5:$E$43,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$34,$A19,Raspored!$E$5:$E$34,"x")</f>
         <v/>
       </c>
       <c r="D19" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$43,$A19,Raspored!$F$5:$F$43,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$34,$A19,Raspored!$F$5:$F$34,"x")</f>
         <v/>
       </c>
       <c r="E19" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$43,$A19,Raspored!$G$5:$G$43,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$34,$A19,Raspored!$G$5:$G$34,"x")</f>
         <v/>
       </c>
     </row>
@@ -950,19 +950,19 @@
         </is>
       </c>
       <c r="B20" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$43,$A20,Raspored!$D$5:$D$43,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$34,$A20,Raspored!$D$5:$D$34,"x")</f>
         <v/>
       </c>
       <c r="C20" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$43,$A20,Raspored!$E$5:$E$43,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$34,$A20,Raspored!$E$5:$E$34,"x")</f>
         <v/>
       </c>
       <c r="D20" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$43,$A20,Raspored!$F$5:$F$43,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$34,$A20,Raspored!$F$5:$F$34,"x")</f>
         <v/>
       </c>
       <c r="E20" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$43,$A20,Raspored!$G$5:$G$43,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$34,$A20,Raspored!$G$5:$G$34,"x")</f>
         <v/>
       </c>
     </row>
@@ -973,19 +973,19 @@
         </is>
       </c>
       <c r="B21" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$43,$A21,Raspored!$D$5:$D$43,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$34,$A21,Raspored!$D$5:$D$34,"x")</f>
         <v/>
       </c>
       <c r="C21" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$43,$A21,Raspored!$E$5:$E$43,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$34,$A21,Raspored!$E$5:$E$34,"x")</f>
         <v/>
       </c>
       <c r="D21" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$43,$A21,Raspored!$F$5:$F$43,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$34,$A21,Raspored!$F$5:$F$34,"x")</f>
         <v/>
       </c>
       <c r="E21" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$43,$A21,Raspored!$G$5:$G$43,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$34,$A21,Raspored!$G$5:$G$34,"x")</f>
         <v/>
       </c>
     </row>
@@ -996,19 +996,19 @@
         </is>
       </c>
       <c r="B22" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$43,$A22,Raspored!$D$5:$D$43,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$34,$A22,Raspored!$D$5:$D$34,"x")</f>
         <v/>
       </c>
       <c r="C22" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$43,$A22,Raspored!$E$5:$E$43,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$34,$A22,Raspored!$E$5:$E$34,"x")</f>
         <v/>
       </c>
       <c r="D22" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$43,$A22,Raspored!$F$5:$F$43,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$34,$A22,Raspored!$F$5:$F$34,"x")</f>
         <v/>
       </c>
       <c r="E22" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$43,$A22,Raspored!$G$5:$G$43,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$34,$A22,Raspored!$G$5:$G$34,"x")</f>
         <v/>
       </c>
     </row>
@@ -1019,19 +1019,19 @@
         </is>
       </c>
       <c r="B23" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$43,$A23,Raspored!$D$5:$D$43,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$34,$A23,Raspored!$D$5:$D$34,"x")</f>
         <v/>
       </c>
       <c r="C23" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$43,$A23,Raspored!$E$5:$E$43,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$34,$A23,Raspored!$E$5:$E$34,"x")</f>
         <v/>
       </c>
       <c r="D23" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$43,$A23,Raspored!$F$5:$F$43,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$34,$A23,Raspored!$F$5:$F$34,"x")</f>
         <v/>
       </c>
       <c r="E23" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$43,$A23,Raspored!$G$5:$G$43,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$34,$A23,Raspored!$G$5:$G$34,"x")</f>
         <v/>
       </c>
     </row>
@@ -1042,19 +1042,19 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$43,$A24,Raspored!$D$5:$D$43,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$34,$A24,Raspored!$D$5:$D$34,"x")</f>
         <v/>
       </c>
       <c r="C24" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$43,$A24,Raspored!$E$5:$E$43,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$34,$A24,Raspored!$E$5:$E$34,"x")</f>
         <v/>
       </c>
       <c r="D24" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$43,$A24,Raspored!$F$5:$F$43,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$34,$A24,Raspored!$F$5:$F$34,"x")</f>
         <v/>
       </c>
       <c r="E24" s="7">
-        <f>COUNTIFS(Raspored!$C$5:$C$43,$A24,Raspored!$G$5:$G$43,"x")</f>
+        <f>COUNTIFS(Raspored!$C$5:$C$34,$A24,Raspored!$G$5:$G$34,"x")</f>
         <v/>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
     <row r="28">
       <c r="A28" s="21" t="inlineStr">
         <is>
-          <t>• Izvor: https://mull-trans.hr/wp-content/uploads/2026/04/OPCINA-KOSKA-raspored-odvoza-otpada-za-2026.pdf (PDF izmijenjen 20.04.2026.)</t>
+          <t>• Od 8.10.2026. odvoz obavlja Urbanizam d.o.o. Valpovo; ovdje je raspored do tada. Izvor: https://mull-trans.hr/wp-content/uploads/2026/04/OPCINA-KOSKA-raspored-odvoza-otpada-za-2026.pdf (PDF izmijenjen 20.04.2026.)</t>
         </is>
       </c>
     </row>
@@ -1155,7 +1155,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H43"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1980,257 +1980,29 @@
       <c r="G34" s="7" t="n"/>
       <c r="H34" s="23" t="n"/>
     </row>
-    <row r="35">
-      <c r="A35" s="6" t="n">
-        <v>46315</v>
-      </c>
-      <c r="B35" s="7" t="inlineStr">
-        <is>
-          <t>utorak</t>
-        </is>
-      </c>
-      <c r="C35" s="7" t="inlineStr">
-        <is>
-          <t>listopad</t>
-        </is>
-      </c>
-      <c r="D35" s="7" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E35" s="7" t="n"/>
-      <c r="F35" s="7" t="n"/>
-      <c r="G35" s="7" t="n"/>
-      <c r="H35" s="23" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="6" t="n">
-        <v>46323</v>
-      </c>
-      <c r="B36" s="7" t="inlineStr">
-        <is>
-          <t>srijeda</t>
-        </is>
-      </c>
-      <c r="C36" s="7" t="inlineStr">
-        <is>
-          <t>listopad</t>
-        </is>
-      </c>
-      <c r="D36" s="7" t="n"/>
-      <c r="E36" s="7" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="F36" s="7" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G36" s="7" t="n"/>
-      <c r="H36" s="23" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="6" t="n">
-        <v>46329</v>
-      </c>
-      <c r="B37" s="7" t="inlineStr">
-        <is>
-          <t>utorak</t>
-        </is>
-      </c>
-      <c r="C37" s="7" t="inlineStr">
-        <is>
-          <t>studeni</t>
-        </is>
-      </c>
-      <c r="D37" s="7" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E37" s="7" t="n"/>
-      <c r="F37" s="7" t="n"/>
-      <c r="G37" s="7" t="n"/>
-      <c r="H37" s="23" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="6" t="n">
-        <v>46343</v>
-      </c>
-      <c r="B38" s="7" t="inlineStr">
-        <is>
-          <t>utorak</t>
-        </is>
-      </c>
-      <c r="C38" s="7" t="inlineStr">
-        <is>
-          <t>studeni</t>
-        </is>
-      </c>
-      <c r="D38" s="7" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E38" s="7" t="n"/>
-      <c r="F38" s="7" t="n"/>
-      <c r="G38" s="7" t="n"/>
-      <c r="H38" s="23" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="6" t="n">
-        <v>46351</v>
-      </c>
-      <c r="B39" s="7" t="inlineStr">
-        <is>
-          <t>srijeda</t>
-        </is>
-      </c>
-      <c r="C39" s="7" t="inlineStr">
-        <is>
-          <t>studeni</t>
-        </is>
-      </c>
-      <c r="D39" s="7" t="n"/>
-      <c r="E39" s="7" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="F39" s="7" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G39" s="7" t="n"/>
-      <c r="H39" s="23" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="6" t="n">
-        <v>46357</v>
-      </c>
-      <c r="B40" s="7" t="inlineStr">
-        <is>
-          <t>utorak</t>
-        </is>
-      </c>
-      <c r="C40" s="7" t="inlineStr">
-        <is>
-          <t>prosinac</t>
-        </is>
-      </c>
-      <c r="D40" s="7" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E40" s="7" t="n"/>
-      <c r="F40" s="7" t="n"/>
-      <c r="G40" s="7" t="n"/>
-      <c r="H40" s="23" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="6" t="n">
-        <v>46371</v>
-      </c>
-      <c r="B41" s="7" t="inlineStr">
-        <is>
-          <t>utorak</t>
-        </is>
-      </c>
-      <c r="C41" s="7" t="inlineStr">
-        <is>
-          <t>prosinac</t>
-        </is>
-      </c>
-      <c r="D41" s="7" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E41" s="7" t="n"/>
-      <c r="F41" s="7" t="n"/>
-      <c r="G41" s="7" t="n"/>
-      <c r="H41" s="23" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="6" t="n">
-        <v>46385</v>
-      </c>
-      <c r="B42" s="7" t="inlineStr">
-        <is>
-          <t>utorak</t>
-        </is>
-      </c>
-      <c r="C42" s="7" t="inlineStr">
-        <is>
-          <t>prosinac</t>
-        </is>
-      </c>
-      <c r="D42" s="7" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E42" s="7" t="n"/>
-      <c r="F42" s="7" t="n"/>
-      <c r="G42" s="7" t="n"/>
-      <c r="H42" s="23" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="6" t="n">
-        <v>46386</v>
-      </c>
-      <c r="B43" s="7" t="inlineStr">
-        <is>
-          <t>srijeda</t>
-        </is>
-      </c>
-      <c r="C43" s="7" t="inlineStr">
-        <is>
-          <t>prosinac</t>
-        </is>
-      </c>
-      <c r="D43" s="7" t="n"/>
-      <c r="E43" s="7" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="F43" s="7" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G43" s="7" t="n"/>
-      <c r="H43" s="23" t="n"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A4:H43"/>
-  <conditionalFormatting sqref="D5:D43">
+  <autoFilter ref="A4:H34"/>
+  <conditionalFormatting sqref="D5:D34">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>D5="x"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E5:E43">
+  <conditionalFormatting sqref="E5:E34">
     <cfRule type="expression" priority="2" dxfId="1">
       <formula>E5="x"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F5:F43">
+  <conditionalFormatting sqref="F5:F34">
     <cfRule type="expression" priority="3" dxfId="2">
       <formula>F5="x"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G5:G43">
+  <conditionalFormatting sqref="G5:G34">
     <cfRule type="expression" priority="4" dxfId="3">
       <formula>G5="x"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A5:H43">
+  <conditionalFormatting sqref="A5:H34">
     <cfRule type="expression" priority="5" dxfId="4" stopIfTrue="0">
       <formula>$A5&lt;TODAY()</formula>
     </cfRule>
@@ -2245,7 +2017,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D52"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2900,200 +2672,8 @@
       </c>
       <c r="D40" s="17" t="n"/>
     </row>
-    <row r="41">
-      <c r="A41" s="24" t="n">
-        <v>46315</v>
-      </c>
-      <c r="B41" s="17" t="inlineStr">
-        <is>
-          <t>utorak</t>
-        </is>
-      </c>
-      <c r="C41" s="5" t="inlineStr">
-        <is>
-          <t>Miješani komunalni otpad</t>
-        </is>
-      </c>
-      <c r="D41" s="17" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="24" t="n">
-        <v>46323</v>
-      </c>
-      <c r="B42" s="17" t="inlineStr">
-        <is>
-          <t>srijeda</t>
-        </is>
-      </c>
-      <c r="C42" s="9" t="inlineStr">
-        <is>
-          <t>Plastika i metal</t>
-        </is>
-      </c>
-      <c r="D42" s="17" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="24" t="n">
-        <v>46323</v>
-      </c>
-      <c r="B43" s="17" t="inlineStr">
-        <is>
-          <t>srijeda</t>
-        </is>
-      </c>
-      <c r="C43" s="10" t="inlineStr">
-        <is>
-          <t>Papir i karton</t>
-        </is>
-      </c>
-      <c r="D43" s="17" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="24" t="n">
-        <v>46329</v>
-      </c>
-      <c r="B44" s="17" t="inlineStr">
-        <is>
-          <t>utorak</t>
-        </is>
-      </c>
-      <c r="C44" s="5" t="inlineStr">
-        <is>
-          <t>Miješani komunalni otpad</t>
-        </is>
-      </c>
-      <c r="D44" s="17" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="24" t="n">
-        <v>46343</v>
-      </c>
-      <c r="B45" s="17" t="inlineStr">
-        <is>
-          <t>utorak</t>
-        </is>
-      </c>
-      <c r="C45" s="5" t="inlineStr">
-        <is>
-          <t>Miješani komunalni otpad</t>
-        </is>
-      </c>
-      <c r="D45" s="17" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="24" t="n">
-        <v>46351</v>
-      </c>
-      <c r="B46" s="17" t="inlineStr">
-        <is>
-          <t>srijeda</t>
-        </is>
-      </c>
-      <c r="C46" s="9" t="inlineStr">
-        <is>
-          <t>Plastika i metal</t>
-        </is>
-      </c>
-      <c r="D46" s="17" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="24" t="n">
-        <v>46351</v>
-      </c>
-      <c r="B47" s="17" t="inlineStr">
-        <is>
-          <t>srijeda</t>
-        </is>
-      </c>
-      <c r="C47" s="10" t="inlineStr">
-        <is>
-          <t>Papir i karton</t>
-        </is>
-      </c>
-      <c r="D47" s="17" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="24" t="n">
-        <v>46357</v>
-      </c>
-      <c r="B48" s="17" t="inlineStr">
-        <is>
-          <t>utorak</t>
-        </is>
-      </c>
-      <c r="C48" s="5" t="inlineStr">
-        <is>
-          <t>Miješani komunalni otpad</t>
-        </is>
-      </c>
-      <c r="D48" s="17" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="24" t="n">
-        <v>46371</v>
-      </c>
-      <c r="B49" s="17" t="inlineStr">
-        <is>
-          <t>utorak</t>
-        </is>
-      </c>
-      <c r="C49" s="5" t="inlineStr">
-        <is>
-          <t>Miješani komunalni otpad</t>
-        </is>
-      </c>
-      <c r="D49" s="17" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="24" t="n">
-        <v>46385</v>
-      </c>
-      <c r="B50" s="17" t="inlineStr">
-        <is>
-          <t>utorak</t>
-        </is>
-      </c>
-      <c r="C50" s="5" t="inlineStr">
-        <is>
-          <t>Miješani komunalni otpad</t>
-        </is>
-      </c>
-      <c r="D50" s="17" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="24" t="n">
-        <v>46386</v>
-      </c>
-      <c r="B51" s="17" t="inlineStr">
-        <is>
-          <t>srijeda</t>
-        </is>
-      </c>
-      <c r="C51" s="9" t="inlineStr">
-        <is>
-          <t>Plastika i metal</t>
-        </is>
-      </c>
-      <c r="D51" s="17" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="24" t="n">
-        <v>46386</v>
-      </c>
-      <c r="B52" s="17" t="inlineStr">
-        <is>
-          <t>srijeda</t>
-        </is>
-      </c>
-      <c r="C52" s="10" t="inlineStr">
-        <is>
-          <t>Papir i karton</t>
-        </is>
-      </c>
-      <c r="D52" s="17" t="n"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:D52"/>
+  <autoFilter ref="A1:D40"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>